--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11775,6 +11775,1178 @@
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>115048550</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>404478</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7012440</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>115048552</v>
+      </c>
+      <c r="B97" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>404584</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7012572</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>115048545</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>404702</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7012430</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>115048546</v>
+      </c>
+      <c r="B99" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>404671</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7012426</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>115048553</v>
+      </c>
+      <c r="B100" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>404588</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7012571</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>115048547</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>404616</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7012423</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>115048551</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>404423</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7012462</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>115048548</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>404623</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7012410</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>115048554</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>405127</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7012351</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>115048556</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79528</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>405178</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7012393</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>115048549</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>404559</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7012397</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -12952,7 +12952,7 @@
         <v>96547675</v>
       </c>
       <c r="B107" t="n">
-        <v>90522</v>
+        <v>90529</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>96547754</v>
       </c>
       <c r="B108" t="n">
-        <v>90522</v>
+        <v>90529</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -12949,7 +12949,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>96547675</v>
+        <v>96547754</v>
       </c>
       <c r="B107" t="n">
         <v>90529</v>
@@ -12990,10 +12990,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>404727</v>
+        <v>404566</v>
       </c>
       <c r="R107" t="n">
-        <v>7012362</v>
+        <v>7012375</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13062,7 +13062,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>96547754</v>
+        <v>96547675</v>
       </c>
       <c r="B108" t="n">
         <v>90529</v>
@@ -13103,10 +13103,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>404566</v>
+        <v>404727</v>
       </c>
       <c r="R108" t="n">
-        <v>7012375</v>
+        <v>7012362</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12947,232 +12947,6 @@
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>96547754</v>
-      </c>
-      <c r="B107" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Åre, Jmt</t>
-        </is>
-      </c>
-      <c r="Q107" t="n">
-        <v>404566</v>
-      </c>
-      <c r="R107" t="n">
-        <v>7012375</v>
-      </c>
-      <c r="S107" t="n">
-        <v>25</v>
-      </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AD107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT107" t="inlineStr"/>
-      <c r="AW107" t="inlineStr">
-        <is>
-          <t>Birgitta Tulin</t>
-        </is>
-      </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>Birgitta Tulin</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>96547675</v>
-      </c>
-      <c r="B108" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Åre, Jmt</t>
-        </is>
-      </c>
-      <c r="Q108" t="n">
-        <v>404727</v>
-      </c>
-      <c r="R108" t="n">
-        <v>7012362</v>
-      </c>
-      <c r="S108" t="n">
-        <v>25</v>
-      </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AD108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT108" t="inlineStr"/>
-      <c r="AW108" t="inlineStr">
-        <is>
-          <t>Birgitta Tulin</t>
-        </is>
-      </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>Birgitta Tulin</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,12 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>79431</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80088</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11687,21 +11682,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80088</v>
+        <v>80092</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80092</v>
+        <v>80096</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80096</v>
+        <v>80001</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80006</v>
+        <v>80007</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80007</v>
+        <v>80011</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80011</v>
+        <v>80013</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80220</v>
+        <v>80221</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80222</v>
+        <v>80224</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>131081607</v>
       </c>
       <c r="B107" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80224</v>
+        <v>80225</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>131081607</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>57728</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80225</v>
+        <v>80226</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>131081607</v>
       </c>
       <c r="B107" t="n">
-        <v>57728</v>
+        <v>57729</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 14183-2021 artfynd.xlsx
+++ b/artfynd/A 14183-2021 artfynd.xlsx
@@ -11674,7 +11674,7 @@
         <v>114462187</v>
       </c>
       <c r="B95" t="n">
-        <v>80226</v>
+        <v>80229</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
